--- a/templates/SoWork-Import-Template.xlsx
+++ b/templates/SoWork-Import-Template.xlsx
@@ -2,15 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jadwal Data" sheetId="1" r:id="R9d9738c1bea240de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist Template" sheetId="2" r:id="R4da8a45718a84c3e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stock Master" sheetId="3" r:id="Ref246c93442f413e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stock Masuk" sheetId="4" r:id="R52fc3374f8304562"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stock Opname" sheetId="5" r:id="R864e0a29f12b49a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Waste Master" sheetId="6" r:id="R85fb990d034c4294"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Waste Harian" sheetId="7" r:id="R355a28a982f24c3d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Laporan" sheetId="8" r:id="Rc775af24bfe544b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="9" r:id="Rb5b8e8bbe3fa4032"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jadwal Data" sheetId="1" r:id="R50cc6b0d14844adf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist Template" sheetId="2" r:id="Rf164e49c7bb04fb5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stock Master" sheetId="3" r:id="Rda4fa2dda70e4aec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stock Masuk" sheetId="4" r:id="Re0bba2ad88044160"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stock Opname" sheetId="5" r:id="Rafd0c20a1a3448d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Waste Master" sheetId="6" r:id="R5f71a657bdca4f99"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Waste Harian" sheetId="7" r:id="R9073978196784c4c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Laporan" sheetId="8" r:id="Rbeedce230d8d4dd5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="9" r:id="R99813029f5ff45b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Penggunaan Stok" sheetId="10" r:id="R5023cd461ef44a14"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -38,12 +39,22 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="6">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF172033"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF8FAFC"/>
+      </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
@@ -63,7 +74,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="18">
+  <x:cellXfs count="27">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -96,6 +107,23 @@
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -384,6 +412,82 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="28" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="36" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="23" t="str">
+        <x:v>Tanggal</x:v>
+      </x:c>
+      <x:c r="B1" s="23" t="str">
+        <x:v>Item ID</x:v>
+      </x:c>
+      <x:c r="C1" s="23" t="str">
+        <x:v>Nama Item</x:v>
+      </x:c>
+      <x:c r="D1" s="23" t="str">
+        <x:v>Qty Digunakan</x:v>
+      </x:c>
+      <x:c r="E1" s="23" t="str">
+        <x:v>Satuan</x:v>
+      </x:c>
+      <x:c r="F1" s="23" t="str">
+        <x:v>Kategori</x:v>
+      </x:c>
+      <x:c r="G1" s="23" t="str">
+        <x:v>Catatan</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="26" t="str">
+        <x:v>2026-09-01</x:v>
+      </x:c>
+      <x:c r="B2" s="26" t="str"/>
+      <x:c r="C2" s="26" t="str">
+        <x:v>Milktea</x:v>
+      </x:c>
+      <x:c r="D2" s="26" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="E2" s="26" t="str">
+        <x:v>GRAM</x:v>
+      </x:c>
+      <x:c r="F2" s="26" t="str">
+        <x:v>Pemakaian Harian</x:v>
+      </x:c>
+      <x:c r="G2" s="26" t="str">
+        <x:v>Produksi normal</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="26" t="str">
+        <x:v>Isi satu baris per item per tanggal. Qty 0 boleh dipakai untuk menandai hari tanpa penggunaan. Import tanggal lama yang sudah melewati Stock Opname terakhir hanya memperbaiki histori/rekonsiliasi dan tidak mengubah current stock.</x:v>
+      </x:c>
+      <x:c r="B4" s="26"/>
+      <x:c r="C4" s="26"/>
+      <x:c r="D4" s="26"/>
+      <x:c r="E4" s="26"/>
+      <x:c r="F4" s="26"/>
+      <x:c r="G4" s="26"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A4:G4"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
@@ -1000,6 +1104,30 @@
       </x:c>
       <x:c r="B4" s="14"/>
     </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>Penggunaan Stok</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>Mengurangi stok sistem per tanggal dan aman diupdate ulang tanpa dobel mengurangi stok.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>Stock Opname</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>Akhir bulan membandingkan stok sistem vs stok fisik; hasil rekonsiliasi tersedia saat export.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>Rumus</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
+        <x:v>SO sebelumnya + Barang Masuk - Penggunaan Harian = Stok Sistem sebelum SO.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A4:B4"/>
